--- a/docs/NORMALIZATION_4FN.xlsx
+++ b/docs/NORMALIZATION_4FN.xlsx
@@ -12,7 +12,6 @@
     <sheet name="Entidades" sheetId="7" r:id="rId7"/>
     <sheet name="Relaciones 4FN" sheetId="8" r:id="rId8"/>
     <sheet name="Restricciones" sheetId="9" r:id="rId9"/>
-    <sheet name="Evidencia" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -408,8 +407,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
   <cols>
-    <col min="1" max="1" width="34.83203125" customWidth="1"/>
-    <col min="2" max="2" width="105.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -422,7 +421,7 @@
         <v>Proyecto</v>
       </c>
       <c r="B2" t="str">
-        <v>Aplicacion monolitica Node.js + Express + EJS + PostgreSQL</v>
+        <v>Aplicación monolítica Node.js + Express + EJS + PostgreSQL</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +437,7 @@
         <v>Objetivo</v>
       </c>
       <c r="B4" t="str">
-        <v>Eliminar grupos repetitivos, dependencias parciales, transitivas y multivaluadas</v>
+        <v>Eliminar datos repetidos, dependencias parciales y multivaluadas</v>
       </c>
     </row>
     <row r="5">
@@ -446,12 +445,12 @@
         <v>Resultado</v>
       </c>
       <c r="B5" t="str">
-        <v>Modelo relacional con tablas puente para autores, generos, imagenes y conceptos</v>
+        <v>Modelo normalizado con tablas puente para autores, géneros, conceptos e imágenes</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Fuente tecnica</v>
+        <v>Fuente técnica</v>
       </c>
       <c r="B6" t="str">
         <v>db/01_schema.sql</v>
@@ -459,7 +458,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Fecha de generacion</v>
+        <v>Fecha de generación</v>
       </c>
       <c r="B7" t="str">
         <v>2026-08-31</v>
@@ -472,119 +471,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="48.83203125" customWidth="1"/>
-    <col min="3" max="3" width="78.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Evidencia</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Comando o archivo</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Que demuestra</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Esquema</v>
-      </c>
-      <c r="B2" t="str">
-        <v>db/01_schema.sql</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Tablas, PK, FK, UNIQUE, CHECK e indices</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Modelo ER</v>
-      </c>
-      <c r="B3" t="str">
-        <v>T2.html -&gt; Descargar PNG</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Entidades y relaciones completas</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Conteos</v>
-      </c>
-      <c r="B4" t="str">
-        <v>db/08_report_evidence.sql</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Cantidad de registros por tabla</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Depuracion</v>
-      </c>
-      <c r="B5" t="str">
-        <v>db/09_cleanup_real_catalog.sql</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Categorias reales y autores sin datos artificiales</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Autores</v>
-      </c>
-      <c r="B6" t="str">
-        <v>db/10_repair_book_authors.sql</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Libros relacionados con autores reales</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Validacion</v>
-      </c>
-      <c r="B7" t="str">
-        <v>npm run verify</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Rutas, assets, busqueda y filtro</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Documentacion</v>
-      </c>
-      <c r="B8" t="str">
-        <v>docs/REQUIREMENTS.md y SECURITY_REVIEW.md</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Requisitos, riesgos y mitigaciones</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:L11"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="50.83203125" customWidth="1"/>
-    <col min="3" max="3" width="50.83203125" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,16 +494,37 @@
         <v>Nivel</v>
       </c>
       <c r="B1" t="str">
-        <v>Situacion</v>
+        <v>Tabla</v>
       </c>
       <c r="C1" t="str">
-        <v>Problema</v>
+        <v>ISBN</v>
       </c>
       <c r="D1" t="str">
-        <v>Accion</v>
+        <v>TITULO</v>
       </c>
       <c r="E1" t="str">
-        <v>Resultado</v>
+        <v>AUTORES</v>
+      </c>
+      <c r="F1" t="str">
+        <v>GENERO</v>
+      </c>
+      <c r="G1" t="str">
+        <v>AÑO</v>
+      </c>
+      <c r="H1" t="str">
+        <v>PRECIO</v>
+      </c>
+      <c r="I1" t="str">
+        <v>STOCK</v>
+      </c>
+      <c r="J1" t="str">
+        <v>FORMATO</v>
+      </c>
+      <c r="K1" t="str">
+        <v>IMAGEN</v>
+      </c>
+      <c r="L1" t="str">
+        <v>CONCEPTOS</v>
       </c>
     </row>
     <row r="2">
@@ -609,16 +532,37 @@
         <v>0FN</v>
       </c>
       <c r="B2" t="str">
-        <v>Un libro contiene varios autores, géneros, imágenes y conceptos en la misma fila</v>
+        <v>libros_desnormalizados</v>
       </c>
       <c r="C2" t="str">
-        <v>Duplicación de datos, inconsistencias y anomalías de inserción</v>
+        <v>9780306406157</v>
       </c>
       <c r="D2" t="str">
-        <v>Separar atributos repetidos en entidades dedicadas</v>
+        <v>IT</v>
       </c>
       <c r="E2" t="str">
-        <v>Base inicial sin normalizar</v>
+        <v>Stephen King</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Terror, Thriller</v>
+      </c>
+      <c r="G2">
+        <v>1986</v>
+      </c>
+      <c r="H2">
+        <v>59.99</v>
+      </c>
+      <c r="I2">
+        <v>29</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Pasta dura</v>
+      </c>
+      <c r="K2" t="str">
+        <v>it.jpg</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Miedo, memoria</v>
       </c>
     </row>
     <row r="3">
@@ -626,387 +570,3907 @@
         <v>0FN</v>
       </c>
       <c r="B3" t="str">
-        <v>Ejemplo de libro desnormalizado</v>
+        <v>libros_desnormalizados</v>
       </c>
       <c r="C3" t="str">
-        <v>Un mismo libro puede duplicarse si cambia autor o género</v>
+        <v>9780451524935</v>
       </c>
       <c r="D3" t="str">
-        <v>Establecer estructura relacional</v>
+        <v>1984</v>
       </c>
       <c r="E3" t="str">
-        <v>Se visualiza la necesidad de 1FN</v>
+        <v>George Orwell</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Distopía, Drama</v>
+      </c>
+      <c r="G3">
+        <v>1949</v>
+      </c>
+      <c r="H3">
+        <v>24.5</v>
+      </c>
+      <c r="I3">
+        <v>18</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Digital EPUB</v>
+      </c>
+      <c r="K3" t="str">
+        <v>1984.jpg</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Poder, libertad</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>0FN</v>
+      </c>
+      <c r="B4" t="str">
+        <v>libros_desnormalizados</v>
+      </c>
+      <c r="C4" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="D4" t="str">
+        <v>The Great Gatsby</v>
+      </c>
+      <c r="E4" t="str">
+        <v>J.K. Rowling</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Novela, Romance</v>
+      </c>
+      <c r="G4">
+        <v>1925</v>
+      </c>
+      <c r="H4">
+        <v>18.9</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Digital PDF</v>
+      </c>
+      <c r="K4" t="str">
+        <v>gatsby.jpg</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Amor, sociedad</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>0FN</v>
+      </c>
+      <c r="B5" t="str">
+        <v>libros_desnormalizados</v>
+      </c>
+      <c r="C5" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Harry Potter y la piedra filosofal</v>
+      </c>
+      <c r="E5" t="str">
+        <v>J.K. Rowling</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Fantasía, Juvenil</v>
+      </c>
+      <c r="G5">
+        <v>1997</v>
+      </c>
+      <c r="H5">
+        <v>34.9</v>
+      </c>
+      <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Pasta dura</v>
+      </c>
+      <c r="K5" t="str">
+        <v>harrypotter.jpg</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Identidad, magia</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>0FN</v>
+      </c>
+      <c r="B6" t="str">
+        <v>libros_desnormalizados</v>
+      </c>
+      <c r="C6" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="D6" t="str">
+        <v>El amor en los tiempos del cólera</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Gabriel García Márquez</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Novela, Drama</v>
+      </c>
+      <c r="G6">
+        <v>1985</v>
+      </c>
+      <c r="H6">
+        <v>20.5</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Digital PDF</v>
+      </c>
+      <c r="K6" t="str">
+        <v>amor-colera.jpg</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Realidad, memoria</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>0FN</v>
+      </c>
+      <c r="B7" t="str">
+        <v>libros_desnormalizados</v>
+      </c>
+      <c r="C7" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Pride and Prejudice</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Jane Austen</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Romance, Novela</v>
+      </c>
+      <c r="G7">
+        <v>1813</v>
+      </c>
+      <c r="H7">
+        <v>17.25</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Digital EPUB</v>
+      </c>
+      <c r="K7" t="str">
+        <v>pride.jpg</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Amor, orgullo</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>0FN</v>
+      </c>
+      <c r="B8" t="str">
+        <v>libros_desnormalizados</v>
+      </c>
+      <c r="C8" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Frankenstein</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Mary Shelley</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Ciencia Ficción, Drama</v>
+      </c>
+      <c r="G8">
+        <v>1818</v>
+      </c>
+      <c r="H8">
+        <v>22.75</v>
+      </c>
+      <c r="I8">
+        <v>14</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Pasta dura</v>
+      </c>
+      <c r="K8" t="str">
+        <v>frankenstein.jpg</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Identidad, moral</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>0FN</v>
+      </c>
+      <c r="B9" t="str">
+        <v>libros_desnormalizados</v>
+      </c>
+      <c r="C9" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Foundation</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Isaac Asimov</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Ciencia Ficción</v>
+      </c>
+      <c r="G9">
+        <v>1951</v>
+      </c>
+      <c r="H9">
+        <v>28.5</v>
+      </c>
+      <c r="I9">
+        <v>17</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Digital EPUB</v>
+      </c>
+      <c r="K9" t="str">
+        <v>foundation.jpg</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Destino, historia</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>0FN</v>
+      </c>
+      <c r="B10" t="str">
+        <v>libros_desnormalizados</v>
+      </c>
+      <c r="C10" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="D10" t="str">
+        <v>La metamorfosis</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Franz Kafka</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Drama, Novela</v>
+      </c>
+      <c r="G10">
+        <v>1915</v>
+      </c>
+      <c r="H10">
+        <v>19.8</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Pasta dura</v>
+      </c>
+      <c r="K10" t="str">
+        <v>metamorfosis.jpg</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Identidad, aislamiento</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>0FN</v>
+      </c>
+      <c r="B11" t="str">
+        <v>libros_desnormalizados</v>
+      </c>
+      <c r="C11" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Mrs Dalloway</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Virginia Woolf</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Novela, Drama</v>
+      </c>
+      <c r="G11">
+        <v>1925</v>
+      </c>
+      <c r="H11">
+        <v>21.4</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Digital PDF</v>
+      </c>
+      <c r="K11" t="str">
+        <v>mrs-dalloway.jpg</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Tiempo, realidad</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:J65"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="42.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
     <col min="3" max="3" width="38.83203125" customWidth="1"/>
-    <col min="4" max="4" width="38.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Regla</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Análisis</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Transformación</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Resultado esperado</v>
+        <v>1FN - Atributos atómicos y separación de entidades</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1FN</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Todos los atributos deben ser atómicos</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Se separan grupos repetitivos en tablas</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Cada valor tiene una fila o una entidad independiente</v>
+        <v>TABLA: authors</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>1FN</v>
+        <v>author_id</v>
       </c>
       <c r="B3" t="str">
-        <v>Generación de tablas base</v>
+        <v>name</v>
       </c>
       <c r="C3" t="str">
-        <v>books, authors, genres, formats, concepts, book_images</v>
+        <v>biography</v>
       </c>
       <c r="D3" t="str">
-        <v>Se elimina la repetición en columnas</v>
+        <v>birth_year</v>
+      </c>
+      <c r="E3" t="str">
+        <v>country</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>1FN</v>
+      <c r="A4">
+        <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>Relaciones N:M</v>
+        <v>Stephen King</v>
       </c>
       <c r="C4" t="str">
-        <v>book_authors, book_genres, book_concepts</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Se crean tablas puente con PK compuesta</v>
+        <v>Autor de terror y fantasía</v>
+      </c>
+      <c r="D4">
+        <v>1947</v>
+      </c>
+      <c r="E4" t="str">
+        <v>United States</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>1FN</v>
+      <c r="A5">
+        <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>Validación</v>
+        <v>George Orwell</v>
       </c>
       <c r="C5" t="str">
-        <v>No existen columnas multi-valoradas ni listas iguales en una fila</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Se cumple 1FN</v>
+        <v>Escritor y periodista británico</v>
+      </c>
+      <c r="D5">
+        <v>1903</v>
+      </c>
+      <c r="E5" t="str">
+        <v>United Kingdom</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>J.K. Rowling</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Autora de fantasía juvenil</v>
+      </c>
+      <c r="D6">
+        <v>1965</v>
+      </c>
+      <c r="E6" t="str">
+        <v>United Kingdom</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Haruki Murakami</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Novelista y escritor japonés</v>
+      </c>
+      <c r="D7">
+        <v>1949</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Japan</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Gabriel García Márquez</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Novelista y periodista colombiano</v>
+      </c>
+      <c r="D8">
+        <v>1927</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Colombia</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Jane Austen</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Novelista inglesa del Romanticismo</v>
+      </c>
+      <c r="D9">
+        <v>1775</v>
+      </c>
+      <c r="E9" t="str">
+        <v>United Kingdom</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Mary Shelley</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Autora inglesa de ciencia ficción</v>
+      </c>
+      <c r="D10">
+        <v>1797</v>
+      </c>
+      <c r="E10" t="str">
+        <v>United Kingdom</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Isaac Asimov</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Escritor y bioquímico estadounidense</v>
+      </c>
+      <c r="D11">
+        <v>1920</v>
+      </c>
+      <c r="E11" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Franz Kafka</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Escritor checo de ficción moderna</v>
+      </c>
+      <c r="D12">
+        <v>1883</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Czech Republic</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Virginia Woolf</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Escritora y crítica británica</v>
+      </c>
+      <c r="D13">
+        <v>1882</v>
+      </c>
+      <c r="E13" t="str">
+        <v>United Kingdom</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TABLA: genres</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>genre_id</v>
+      </c>
+      <c r="B16" t="str">
+        <v>name</v>
+      </c>
+      <c r="C16" t="str">
+        <v>description</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Terror</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Obras de tensión, misterio y miedo</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Ciencia Ficción</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Narrativas basadas en tecnología y futuro</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Fantasía</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Mundos imaginarios y magia</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Novela</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Ficción narrativa extensa</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Distopía</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Sociedades futuristas controladas</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>6</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Romance</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Relaciones y desarrollo emocional</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>7</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Historia</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Narrativas históricas o documentales</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Drama</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Obras con tensión psicológica y emocional</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>9</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Filosofía</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Temas conceptuales y reflexivos</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>10</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Misterio</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Enigmas y resolución de casos</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TABLA: formats</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>format_id</v>
+      </c>
+      <c r="B29" t="str">
+        <v>name</v>
+      </c>
+      <c r="C29" t="str">
+        <v>description</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Físico</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Edición tradicional impresa</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Digital PDF</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Formato PDF para lectura digital</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Digital EPUB</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Formato EPUB para lector electrónico</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Audiolibro</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Versión sonora del libro</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Colección</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Edición especial de colección</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>6</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Bolsillo</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Formato compacto y portable</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>7</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Premium</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Edición de lujo</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>8</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Edición institucional</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>9</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Pasta Dura</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Edición de cubierta rígida</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>10</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Pasta Blanda</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Edición de cubierta blanda</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TABLA: concepts</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>concept_id</v>
+      </c>
+      <c r="B42" t="str">
+        <v>name</v>
+      </c>
+      <c r="C42" t="str">
+        <v>description</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Identidad</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Cómo se define la personalidad de los personajes</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Tiempo</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Relación entre hechos y secuencia narrativa</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Tecnología</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Uso de avances científicos en la historia</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>4</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Poder</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Influencias políticas, sociales y morales</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>5</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Memoria</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Recuerdos y su impacto en la trama</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>6</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Libertad</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Elección individual frente a control externo</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>7</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Miedo</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Emoción que impulsa tensión y suspense</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>8</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Amor</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Relaciones humanas y emoción</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>9</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Realidad</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Distinción entre hecho objetivo y percepción</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>10</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Destino</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Curso inevitable de los acontecimientos</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TABLA: books</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="B55" t="str">
+        <v>title</v>
+      </c>
+      <c r="C55" t="str">
+        <v>description</v>
+      </c>
+      <c r="D55" t="str">
+        <v>publication_year</v>
+      </c>
+      <c r="E55" t="str">
+        <v>price</v>
+      </c>
+      <c r="F55" t="str">
+        <v>stock</v>
+      </c>
+      <c r="G55" t="str">
+        <v>format_id</v>
+      </c>
+      <c r="H55" t="str">
+        <v>format_type</v>
+      </c>
+      <c r="I55" t="str">
+        <v>digital_format</v>
+      </c>
+      <c r="J55" t="str">
+        <v>publisher</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B56" t="str">
+        <v>IT</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Historia de un grupo de amigos que enfrentan a un enemigo ancestral</v>
+      </c>
+      <c r="D56">
+        <v>1986</v>
+      </c>
+      <c r="E56">
+        <v>59.99</v>
+      </c>
+      <c r="F56">
+        <v>29</v>
+      </c>
+      <c r="G56">
+        <v>10</v>
+      </c>
+      <c r="H56" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Scribner</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B57" t="str">
+        <v>1984</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Una distopía sobre vigilancia y manipulación del pensamiento</v>
+      </c>
+      <c r="D57">
+        <v>1949</v>
+      </c>
+      <c r="E57">
+        <v>24.5</v>
+      </c>
+      <c r="F57">
+        <v>18</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I57" t="str">
+        <v>EPUB</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Secker &amp; Warburg</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B58" t="str">
+        <v>The Great Gatsby</v>
+      </c>
+      <c r="C58" t="str">
+        <v>La decadencia de la riqueza y el sueño americano</v>
+      </c>
+      <c r="D58">
+        <v>1925</v>
+      </c>
+      <c r="E58">
+        <v>18.9</v>
+      </c>
+      <c r="F58">
+        <v>12</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I58" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Scribner</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Harry Potter y la piedra filosofal</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Un niño descubre su magia y es aceptado en Hogwarts</v>
+      </c>
+      <c r="D59">
+        <v>1997</v>
+      </c>
+      <c r="E59">
+        <v>34.9</v>
+      </c>
+      <c r="F59">
+        <v>26</v>
+      </c>
+      <c r="G59">
+        <v>10</v>
+      </c>
+      <c r="H59" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Bloomsbury</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B60" t="str">
+        <v>El amor en los tiempos del cólera</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Elegía sobre el amor, la espera y el destino</v>
+      </c>
+      <c r="D60">
+        <v>1985</v>
+      </c>
+      <c r="E60">
+        <v>20.5</v>
+      </c>
+      <c r="F60">
+        <v>15</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I60" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Random House</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Pride and Prejudice</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Relaciones sociales y evolución emocional en la Inglaterra del siglo XIX</v>
+      </c>
+      <c r="D61">
+        <v>1813</v>
+      </c>
+      <c r="E61">
+        <v>17.25</v>
+      </c>
+      <c r="F61">
+        <v>11</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I61" t="str">
+        <v>EPUB</v>
+      </c>
+      <c r="J61" t="str">
+        <v>Penguin</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Frankenstein</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Una creación científica y la responsabilidad moral del hombre</v>
+      </c>
+      <c r="D62">
+        <v>1818</v>
+      </c>
+      <c r="E62">
+        <v>22.75</v>
+      </c>
+      <c r="F62">
+        <v>14</v>
+      </c>
+      <c r="G62">
+        <v>9</v>
+      </c>
+      <c r="H62" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J62" t="str">
+        <v>Oxford</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Foundation</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Una civilización intenta proteger su futuro frente a la decadencia</v>
+      </c>
+      <c r="D63">
+        <v>1951</v>
+      </c>
+      <c r="E63">
+        <v>28.5</v>
+      </c>
+      <c r="F63">
+        <v>17</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I63" t="str">
+        <v>EPUB</v>
+      </c>
+      <c r="J63" t="str">
+        <v>Gnome Press</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="B64" t="str">
+        <v>La metamorfosis</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Un viajero despierta transformado y aislado de su familia</v>
+      </c>
+      <c r="D64">
+        <v>1915</v>
+      </c>
+      <c r="E64">
+        <v>19.8</v>
+      </c>
+      <c r="F64">
+        <v>9</v>
+      </c>
+      <c r="G64">
+        <v>10</v>
+      </c>
+      <c r="H64" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J64" t="str">
+        <v>Schocken</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Mrs Dalloway</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Una jornada íntima en la vida de una mujer londinense</v>
+      </c>
+      <c r="D65">
+        <v>1925</v>
+      </c>
+      <c r="E65">
+        <v>21.4</v>
+      </c>
+      <c r="F65">
+        <v>10</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I65" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Harcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J65"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:C52"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="44.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Regla</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Análisis</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Observación</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Resultado esperado</v>
+        <v>2FN - Todas las claves no primarias dependen de la clave compuesta</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2FN</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Es necesario que todo atributo no clave dependa de toda la clave primaria</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Las tablas puente usan clave primaria compuesta</v>
-      </c>
-      <c r="D2" t="str">
-        <v>No hay dependencia parcial</v>
+        <v>TABLA: book_authors</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2FN</v>
+        <v>isbn</v>
       </c>
       <c r="B3" t="str">
-        <v>book_authors</v>
-      </c>
-      <c r="C3" t="str">
-        <v>(isbn, author_id) y los atributos no clave son nulos o no aplican</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Todo valor depende del conjunto completo de la clave</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Se cumple 2FN</v>
+        <v>author_id</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2FN</v>
-      </c>
-      <c r="B4" t="str">
-        <v>book_genres</v>
-      </c>
-      <c r="C4" t="str">
-        <v>(isbn, genre_id) cumple la misma regla</v>
-      </c>
-      <c r="D4" t="str">
-        <v>No hay atributos que dependan solo de isbn o solo de genre_id</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Se cumple 2FN</v>
+        <v>9780306406157</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2FN</v>
-      </c>
-      <c r="B5" t="str">
-        <v>book_concepts</v>
-      </c>
-      <c r="C5" t="str">
-        <v>(isbn, concept_id) conserva definición y relación</v>
-      </c>
-      <c r="D5" t="str">
-        <v>La definición depende del par completo</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Se cumple 2FN</v>
+        <v>9780451524935</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TABLA: book_genres</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="B21" t="str">
+        <v>genre_id</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TABLA: book_concepts</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="B39" t="str">
+        <v>concept_id</v>
+      </c>
+      <c r="C39" t="str">
+        <v>definition</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B40">
+        <v>7</v>
+      </c>
+      <c r="C40" t="str">
+        <v>El miedo se convierte en un mecanismo de control emocional y social</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B41">
+        <v>5</v>
+      </c>
+      <c r="C41" t="str">
+        <v>La memoria del pasado tiene poder sobre la identidad de una comunidad</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42" t="str">
+        <v>El poder totalitario se sostiene en la vigilancia y la manipulación</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B43">
+        <v>6</v>
+      </c>
+      <c r="C43" t="str">
+        <v>La libertad individual se enfrenta con la disciplina social</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+      <c r="C44" t="str">
+        <v>El amor y la clase social condicionan la percepción de la felicidad</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B45">
+        <v>3</v>
+      </c>
+      <c r="C45" t="str">
+        <v>La tecnología y la magia conforman la identidad del mundo fantástico</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" t="str">
+        <v>La identidad del protagonista se define por su pertenencia a Hogwarts</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B47">
+        <v>9</v>
+      </c>
+      <c r="C47" t="str">
+        <v>La realidad se percibe de manera distinta según la memoria y la esperanza</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="B48">
+        <v>8</v>
+      </c>
+      <c r="C48" t="str">
+        <v>El amor y el orgullo alteran las decisiones humanas</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="str">
+        <v>La creación despierta una crisis ética y emocional en el creador</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="B50">
+        <v>10</v>
+      </c>
+      <c r="C50" t="str">
+        <v>El destino de la civilización parece inevitable ante el ciclo histórico</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="str">
+        <v>La identidad personal se transforma al perder la relación familiar</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52" t="str">
+        <v>El paso del tiempo orienta la percepción del mundo interno de la protagonista</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C52"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:J39"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
-    <col min="4" max="4" width="38.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Regla</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Análisis</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Observación</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Resultado esperado</v>
+        <v>3FN - Sin dependencias transitivas</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>3FN</v>
-      </c>
-      <c r="B2" t="str">
-        <v>No debe haber dependencias transitivas</v>
-      </c>
-      <c r="C2" t="str">
-        <v>El formato o catálogo no depende de otra columna no clave</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Se separa catálogo de formatos</v>
+        <v>TABLA: books</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>3FN</v>
+        <v>isbn</v>
       </c>
       <c r="B3" t="str">
-        <v>books</v>
+        <v>title</v>
       </c>
       <c r="C3" t="str">
-        <v>isbn determina título, precio, stock, editorial y formato</v>
+        <v>description</v>
       </c>
       <c r="D3" t="str">
-        <v>La dependencia es directa con la PK</v>
+        <v>publication_year</v>
       </c>
       <c r="E3" t="str">
-        <v>Se cumple 3FN</v>
+        <v>price</v>
+      </c>
+      <c r="F3" t="str">
+        <v>stock</v>
+      </c>
+      <c r="G3" t="str">
+        <v>format_id</v>
+      </c>
+      <c r="H3" t="str">
+        <v>format_type</v>
+      </c>
+      <c r="I3" t="str">
+        <v>digital_format</v>
+      </c>
+      <c r="J3" t="str">
+        <v>publisher</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3FN</v>
+        <v>9780306406157</v>
       </c>
       <c r="B4" t="str">
-        <v>formats</v>
+        <v>IT</v>
       </c>
       <c r="C4" t="str">
-        <v>format_id determina nombre del formato</v>
-      </c>
-      <c r="D4" t="str">
-        <v>No existe un atributo ajeno que lo controle</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Se cumple 3FN</v>
+        <v>Historia de un grupo de amigos que enfrentan a un enemigo ancestral</v>
+      </c>
+      <c r="D4">
+        <v>1986</v>
+      </c>
+      <c r="E4">
+        <v>59.99</v>
+      </c>
+      <c r="F4">
+        <v>29</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Scribner</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>3FN</v>
+        <v>9780451524935</v>
       </c>
       <c r="B5" t="str">
-        <v>concepts</v>
+        <v>1984</v>
       </c>
       <c r="C5" t="str">
-        <v>concept_id determina nombre del concepto</v>
-      </c>
-      <c r="D5" t="str">
-        <v>No se repite la misma definición en varias filas</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Se cumple 3FN</v>
+        <v>Una distopía sobre vigilancia y manipulación del pensamiento</v>
+      </c>
+      <c r="D5">
+        <v>1949</v>
+      </c>
+      <c r="E5">
+        <v>24.5</v>
+      </c>
+      <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I5" t="str">
+        <v>EPUB</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Secker &amp; Warburg</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B6" t="str">
+        <v>The Great Gatsby</v>
+      </c>
+      <c r="C6" t="str">
+        <v>La decadencia de la riqueza y el sueño americano</v>
+      </c>
+      <c r="D6">
+        <v>1925</v>
+      </c>
+      <c r="E6">
+        <v>18.9</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I6" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Scribner</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Harry Potter y la piedra filosofal</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Un niño descubre su magia y es aceptado en Hogwarts</v>
+      </c>
+      <c r="D7">
+        <v>1997</v>
+      </c>
+      <c r="E7">
+        <v>34.9</v>
+      </c>
+      <c r="F7">
+        <v>26</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Bloomsbury</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B8" t="str">
+        <v>El amor en los tiempos del cólera</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Elegía sobre el amor, la espera y el destino</v>
+      </c>
+      <c r="D8">
+        <v>1985</v>
+      </c>
+      <c r="E8">
+        <v>20.5</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I8" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Random House</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Pride and Prejudice</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Relaciones sociales y evolución emocional en la Inglaterra del siglo XIX</v>
+      </c>
+      <c r="D9">
+        <v>1813</v>
+      </c>
+      <c r="E9">
+        <v>17.25</v>
+      </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I9" t="str">
+        <v>EPUB</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Penguin</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Frankenstein</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Una creación científica y la responsabilidad moral del hombre</v>
+      </c>
+      <c r="D10">
+        <v>1818</v>
+      </c>
+      <c r="E10">
+        <v>22.75</v>
+      </c>
+      <c r="F10">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Oxford</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Foundation</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Una civilización intenta proteger su futuro frente a la decadencia</v>
+      </c>
+      <c r="D11">
+        <v>1951</v>
+      </c>
+      <c r="E11">
+        <v>28.5</v>
+      </c>
+      <c r="F11">
+        <v>17</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I11" t="str">
+        <v>EPUB</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Gnome Press</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="B12" t="str">
+        <v>La metamorfosis</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Un viajero despierta transformado y aislado de su familia</v>
+      </c>
+      <c r="D12">
+        <v>1915</v>
+      </c>
+      <c r="E12">
+        <v>19.8</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Schocken</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Mrs Dalloway</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Una jornada íntima en la vida de una mujer londinense</v>
+      </c>
+      <c r="D13">
+        <v>1925</v>
+      </c>
+      <c r="E13">
+        <v>21.4</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I13" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Harcourt</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TABLA: formats</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>format_id</v>
+      </c>
+      <c r="B16" t="str">
+        <v>name</v>
+      </c>
+      <c r="C16" t="str">
+        <v>description</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Físico</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Edición tradicional impresa</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Digital PDF</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Formato PDF para lectura digital</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Digital EPUB</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Formato EPUB para lector electrónico</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Audiolibro</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Versión sonora del libro</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Colección</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Edición especial de colección</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>6</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Bolsillo</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Formato compacto y portable</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>7</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Premium</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Edición de lujo</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Campus</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Edición institucional</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>9</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Pasta Dura</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Edición de cubierta rígida</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>10</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Pasta Blanda</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Edición de cubierta blanda</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TABLA: concepts</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>concept_id</v>
+      </c>
+      <c r="B29" t="str">
+        <v>name</v>
+      </c>
+      <c r="C29" t="str">
+        <v>description</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Identidad</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Cómo se define la personalidad de los personajes</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Tiempo</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Relación entre hechos y secuencia narrativa</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Tecnología</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Uso de avances científicos en la historia</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Poder</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Influencias políticas, sociales y morales</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Memoria</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Recuerdos y su impacto en la trama</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>6</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Libertad</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Elección individual frente a control externo</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>7</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Miedo</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Emoción que impulsa tensión y suspense</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>8</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Amor</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Relaciones humanas y emoción</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>9</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Realidad</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Distinción entre hecho objetivo y percepción</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>10</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Destino</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Curso inevitable de los acontecimientos</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:J108"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="44.83203125" customWidth="1"/>
-    <col min="3" max="3" width="44.83203125" customWidth="1"/>
-    <col min="4" max="4" width="38.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="80.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Regla</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Análisis</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Problema resuelto</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Resultado esperado</v>
+        <v>4FN - Eliminación de dependencias multivaluadas y diccionario de datos</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>4FN</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Se eliminan dependencias multivaluadas no triviales</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Un libro puede tener varios autores y varios géneros independientemente</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Se separan las relaciones como entidades independientes</v>
+        <v>TABLA: books</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>4FN</v>
+        <v>isbn</v>
       </c>
       <c r="B3" t="str">
-        <v>MVD</v>
+        <v>title</v>
       </c>
       <c r="C3" t="str">
-        <v>Si un libro posee 3 autores y 2 géneros, no se genera 6 filas redundantes en una sola tabla</v>
+        <v>description</v>
       </c>
       <c r="D3" t="str">
-        <v>Se usa book_authors y book_genres</v>
+        <v>publication_year</v>
+      </c>
+      <c r="E3" t="str">
+        <v>price</v>
+      </c>
+      <c r="F3" t="str">
+        <v>stock</v>
+      </c>
+      <c r="G3" t="str">
+        <v>format_id</v>
+      </c>
+      <c r="H3" t="str">
+        <v>format_type</v>
+      </c>
+      <c r="I3" t="str">
+        <v>digital_format</v>
+      </c>
+      <c r="J3" t="str">
+        <v>publisher</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>4FN</v>
+        <v>9780306406157</v>
       </c>
       <c r="B4" t="str">
-        <v>Aplicación del diseño</v>
+        <v>IT</v>
       </c>
       <c r="C4" t="str">
-        <v>book_images y book_concepts se mantienen como relaciones independientes</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Se evita producto cartesiano y redundancia</v>
+        <v>Historia de un grupo de amigos que enfrentan a un enemigo ancestral</v>
+      </c>
+      <c r="D4">
+        <v>1986</v>
+      </c>
+      <c r="E4">
+        <v>59.99</v>
+      </c>
+      <c r="F4">
+        <v>29</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Scribner</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4FN</v>
+        <v>9780451524935</v>
       </c>
       <c r="B5" t="str">
-        <v>Resultado final</v>
+        <v>1984</v>
       </c>
       <c r="C5" t="str">
-        <v>Base de datos normalizada a 4FN</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Modelo estable para CRUD, búsquedas y validación</v>
+        <v>Una distopía sobre vigilancia y manipulación del pensamiento</v>
+      </c>
+      <c r="D5">
+        <v>1949</v>
+      </c>
+      <c r="E5">
+        <v>24.5</v>
+      </c>
+      <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I5" t="str">
+        <v>EPUB</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Secker &amp; Warburg</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B6" t="str">
+        <v>The Great Gatsby</v>
+      </c>
+      <c r="C6" t="str">
+        <v>La decadencia de la riqueza y el sueño americano</v>
+      </c>
+      <c r="D6">
+        <v>1925</v>
+      </c>
+      <c r="E6">
+        <v>18.9</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I6" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Scribner</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Harry Potter y la piedra filosofal</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Un niño descubre su magia y es aceptado en Hogwarts</v>
+      </c>
+      <c r="D7">
+        <v>1997</v>
+      </c>
+      <c r="E7">
+        <v>34.9</v>
+      </c>
+      <c r="F7">
+        <v>26</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Bloomsbury</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B8" t="str">
+        <v>El amor en los tiempos del cólera</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Elegía sobre el amor, la espera y el destino</v>
+      </c>
+      <c r="D8">
+        <v>1985</v>
+      </c>
+      <c r="E8">
+        <v>20.5</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I8" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Random House</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Pride and Prejudice</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Relaciones sociales y evolución emocional en la Inglaterra del siglo XIX</v>
+      </c>
+      <c r="D9">
+        <v>1813</v>
+      </c>
+      <c r="E9">
+        <v>17.25</v>
+      </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I9" t="str">
+        <v>EPUB</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Penguin</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Frankenstein</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Una creación científica y la responsabilidad moral del hombre</v>
+      </c>
+      <c r="D10">
+        <v>1818</v>
+      </c>
+      <c r="E10">
+        <v>22.75</v>
+      </c>
+      <c r="F10">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Oxford</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Foundation</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Una civilización intenta proteger su futuro frente a la decadencia</v>
+      </c>
+      <c r="D11">
+        <v>1951</v>
+      </c>
+      <c r="E11">
+        <v>28.5</v>
+      </c>
+      <c r="F11">
+        <v>17</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I11" t="str">
+        <v>EPUB</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Gnome Press</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="B12" t="str">
+        <v>La metamorfosis</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Un viajero despierta transformado y aislado de su familia</v>
+      </c>
+      <c r="D12">
+        <v>1915</v>
+      </c>
+      <c r="E12">
+        <v>19.8</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12" t="str">
+        <v>PHYSICAL</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Schocken</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Mrs Dalloway</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Una jornada íntima en la vida de una mujer londinense</v>
+      </c>
+      <c r="D13">
+        <v>1925</v>
+      </c>
+      <c r="E13">
+        <v>21.4</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="str">
+        <v>DIGITAL</v>
+      </c>
+      <c r="I13" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Harcourt</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TABLA: book_authors</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="B16" t="str">
+        <v>author_id</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TABLA: book_genres</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="B34" t="str">
+        <v>genre_id</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="B45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="B48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="B49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TABLA: book_concepts</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="B52" t="str">
+        <v>concept_id</v>
+      </c>
+      <c r="C52" t="str">
+        <v>definition</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
+      </c>
+      <c r="C53" t="str">
+        <v>El miedo se convierte en un mecanismo de control emocional y social</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="B54">
+        <v>5</v>
+      </c>
+      <c r="C54" t="str">
+        <v>La memoria del pasado tiene poder sobre la identidad de una comunidad</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55" t="str">
+        <v>El poder totalitario se sostiene en la vigilancia y la manipulación</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="B56">
+        <v>6</v>
+      </c>
+      <c r="C56" t="str">
+        <v>La libertad individual se enfrenta con la disciplina social</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="B57">
+        <v>8</v>
+      </c>
+      <c r="C57" t="str">
+        <v>El amor y la clase social condicionan la percepción de la felicidad</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B58">
+        <v>3</v>
+      </c>
+      <c r="C58" t="str">
+        <v>La tecnología y la magia conforman la identidad del mundo fantástico</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="str">
+        <v>La identidad del protagonista se define por su pertenencia a Hogwarts</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="B60">
+        <v>9</v>
+      </c>
+      <c r="C60" t="str">
+        <v>La realidad se percibe de manera distinta según la memoria y la esperanza</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61" t="str">
+        <v>El amor y el orgullo alteran las decisiones humanas</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="str">
+        <v>La creación despierta una crisis ética y emocional en el creador</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="B63">
+        <v>10</v>
+      </c>
+      <c r="C63" t="str">
+        <v>El destino de la civilización parece inevitable ante el ciclo histórico</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64" t="str">
+        <v>La identidad personal se transforma al perder la relación familiar</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65" t="str">
+        <v>El paso del tiempo orienta la percepción del mundo interno de la protagonista</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>TABLA: book_images</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>image_id</v>
+      </c>
+      <c r="B68" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="C68" t="str">
+        <v>image_url</v>
+      </c>
+      <c r="D68" t="str">
+        <v>alt_text</v>
+      </c>
+      <c r="E68" t="str">
+        <v>is_cover</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>1</v>
+      </c>
+      <c r="B69" t="str">
+        <v>9780306406157</v>
+      </c>
+      <c r="C69" t="str">
+        <v>/uploads/it.jpg</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Portada IT</v>
+      </c>
+      <c r="E69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>2</v>
+      </c>
+      <c r="B70" t="str">
+        <v>9780451524935</v>
+      </c>
+      <c r="C70" t="str">
+        <v>/uploads/1984.jpg</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Portada 1984</v>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>3</v>
+      </c>
+      <c r="B71" t="str">
+        <v>9780743273565</v>
+      </c>
+      <c r="C71" t="str">
+        <v>/uploads/gatsby.jpg</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Portada Great Gatsby</v>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>4</v>
+      </c>
+      <c r="B72" t="str">
+        <v>9780439708180</v>
+      </c>
+      <c r="C72" t="str">
+        <v>/uploads/harrypotter.jpg</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Portada Harry Potter</v>
+      </c>
+      <c r="E72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73" t="str">
+        <v>9780679775430</v>
+      </c>
+      <c r="C73" t="str">
+        <v>/uploads/amor-colera.jpg</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Portada El amor en los tiempos del cólera</v>
+      </c>
+      <c r="E73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>6</v>
+      </c>
+      <c r="B74" t="str">
+        <v>9780141439518</v>
+      </c>
+      <c r="C74" t="str">
+        <v>/uploads/pride.jpg</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Portada Pride and Prejudice</v>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>7</v>
+      </c>
+      <c r="B75" t="str">
+        <v>9780199535569</v>
+      </c>
+      <c r="C75" t="str">
+        <v>/uploads/frankenstein.jpg</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Portada Frankenstein</v>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>8</v>
+      </c>
+      <c r="B76" t="str">
+        <v>9780553382575</v>
+      </c>
+      <c r="C76" t="str">
+        <v>/uploads/foundation.jpg</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Portada Foundation</v>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>9</v>
+      </c>
+      <c r="B77" t="str">
+        <v>9780805211063</v>
+      </c>
+      <c r="C77" t="str">
+        <v>/uploads/metamorfosis.jpg</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Portada La metamorfosis</v>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>10</v>
+      </c>
+      <c r="B78" t="str">
+        <v>9780156028356</v>
+      </c>
+      <c r="C78" t="str">
+        <v>/uploads/mrs-dalloway.jpg</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Portada Mrs Dalloway</v>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>DICCIONARIO DE DATOS</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Tabla</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Clave</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Descripcion</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Regla/Validacion</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>books</v>
+      </c>
+      <c r="B82" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="C82" t="str">
+        <v>VARCHAR(20)</v>
+      </c>
+      <c r="D82" t="str">
+        <v>PK</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Identificador único del libro</v>
+      </c>
+      <c r="F82" t="str">
+        <v>No nulo y único</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>books</v>
+      </c>
+      <c r="B83" t="str">
+        <v>title</v>
+      </c>
+      <c r="C83" t="str">
+        <v>VARCHAR(255)</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v>Título del libro</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Obligatorio</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>books</v>
+      </c>
+      <c r="B84" t="str">
+        <v>description</v>
+      </c>
+      <c r="C84" t="str">
+        <v>TEXT</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v>Resumen del contenido</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Puede ser nulo</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>books</v>
+      </c>
+      <c r="B85" t="str">
+        <v>publication_year</v>
+      </c>
+      <c r="C85" t="str">
+        <v>INTEGER</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v>Año de publicación</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Puede ser nulo</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>books</v>
+      </c>
+      <c r="B86" t="str">
+        <v>price</v>
+      </c>
+      <c r="C86" t="str">
+        <v>DECIMAL(10,2)</v>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v>Precio del libro</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Debe ser &gt;= 0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>books</v>
+      </c>
+      <c r="B87" t="str">
+        <v>stock</v>
+      </c>
+      <c r="C87" t="str">
+        <v>INTEGER</v>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v>Existencias disponibles</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Debe ser &gt;= 0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>books</v>
+      </c>
+      <c r="B88" t="str">
+        <v>format_id</v>
+      </c>
+      <c r="C88" t="str">
+        <v>INTEGER</v>
+      </c>
+      <c r="D88" t="str">
+        <v>FK</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Identificador del formato</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Referencias formats(format_id)</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>books</v>
+      </c>
+      <c r="B89" t="str">
+        <v>format_type</v>
+      </c>
+      <c r="C89" t="str">
+        <v>VARCHAR(20)</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v>Tipo de edición</v>
+      </c>
+      <c r="F89" t="str">
+        <v>PHYSICAL o DIGITAL</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>books</v>
+      </c>
+      <c r="B90" t="str">
+        <v>digital_format</v>
+      </c>
+      <c r="C90" t="str">
+        <v>VARCHAR(10)</v>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v>Formato digital</v>
+      </c>
+      <c r="F90" t="str">
+        <v>PDF o EPUB</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>books</v>
+      </c>
+      <c r="B91" t="str">
+        <v>publisher</v>
+      </c>
+      <c r="C91" t="str">
+        <v>VARCHAR(150)</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v>Editorial</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Puede ser nulo</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>authors</v>
+      </c>
+      <c r="B92" t="str">
+        <v>author_id</v>
+      </c>
+      <c r="C92" t="str">
+        <v>SERIAL</v>
+      </c>
+      <c r="D92" t="str">
+        <v>PK</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Identificador de autor</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Autonumérico</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>authors</v>
+      </c>
+      <c r="B93" t="str">
+        <v>name</v>
+      </c>
+      <c r="C93" t="str">
+        <v>VARCHAR(150)</v>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v>Nombre del autor</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Obligatorio</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>authors</v>
+      </c>
+      <c r="B94" t="str">
+        <v>biography</v>
+      </c>
+      <c r="C94" t="str">
+        <v>TEXT</v>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v>Biografía del autor</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Puede ser nulo</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>authors</v>
+      </c>
+      <c r="B95" t="str">
+        <v>birth_year</v>
+      </c>
+      <c r="C95" t="str">
+        <v>INTEGER</v>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v>Año de nacimiento</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Puede ser nulo</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>authors</v>
+      </c>
+      <c r="B96" t="str">
+        <v>country</v>
+      </c>
+      <c r="C96" t="str">
+        <v>VARCHAR(100)</v>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v>País de origen</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Puede ser nulo</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>book_authors</v>
+      </c>
+      <c r="B97" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="C97" t="str">
+        <v>VARCHAR(20)</v>
+      </c>
+      <c r="D97" t="str">
+        <v>PK/FK</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Libro relacionado</v>
+      </c>
+      <c r="F97" t="str">
+        <v>FK a books(isbn)</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>book_authors</v>
+      </c>
+      <c r="B98" t="str">
+        <v>author_id</v>
+      </c>
+      <c r="C98" t="str">
+        <v>INTEGER</v>
+      </c>
+      <c r="D98" t="str">
+        <v>PK/FK</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Autor relacionado</v>
+      </c>
+      <c r="F98" t="str">
+        <v>FK a authors(author_id)</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>book_genres</v>
+      </c>
+      <c r="B99" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="C99" t="str">
+        <v>VARCHAR(20)</v>
+      </c>
+      <c r="D99" t="str">
+        <v>PK/FK</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Libro relacionado</v>
+      </c>
+      <c r="F99" t="str">
+        <v>FK a books(isbn)</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>book_genres</v>
+      </c>
+      <c r="B100" t="str">
+        <v>genre_id</v>
+      </c>
+      <c r="C100" t="str">
+        <v>INTEGER</v>
+      </c>
+      <c r="D100" t="str">
+        <v>PK/FK</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Género asociado</v>
+      </c>
+      <c r="F100" t="str">
+        <v>FK a genres(genre_id)</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>book_concepts</v>
+      </c>
+      <c r="B101" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="C101" t="str">
+        <v>VARCHAR(20)</v>
+      </c>
+      <c r="D101" t="str">
+        <v>PK/FK</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Libro relacionado</v>
+      </c>
+      <c r="F101" t="str">
+        <v>FK a books(isbn)</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>book_concepts</v>
+      </c>
+      <c r="B102" t="str">
+        <v>concept_id</v>
+      </c>
+      <c r="C102" t="str">
+        <v>INTEGER</v>
+      </c>
+      <c r="D102" t="str">
+        <v>PK/FK</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Concepto asociado</v>
+      </c>
+      <c r="F102" t="str">
+        <v>FK a concepts(concept_id)</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>book_concepts</v>
+      </c>
+      <c r="B103" t="str">
+        <v>definition</v>
+      </c>
+      <c r="C103" t="str">
+        <v>TEXT</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v>Definición del concepto</v>
+      </c>
+      <c r="F103" t="str">
+        <v>No nulo</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>book_images</v>
+      </c>
+      <c r="B104" t="str">
+        <v>image_id</v>
+      </c>
+      <c r="C104" t="str">
+        <v>SERIAL</v>
+      </c>
+      <c r="D104" t="str">
+        <v>PK</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Identificador de imagen</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Autonumérico</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>book_images</v>
+      </c>
+      <c r="B105" t="str">
+        <v>isbn</v>
+      </c>
+      <c r="C105" t="str">
+        <v>VARCHAR(20)</v>
+      </c>
+      <c r="D105" t="str">
+        <v>FK</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Libro asociado</v>
+      </c>
+      <c r="F105" t="str">
+        <v>FK a books(isbn)</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>book_images</v>
+      </c>
+      <c r="B106" t="str">
+        <v>image_url</v>
+      </c>
+      <c r="C106" t="str">
+        <v>VARCHAR(500)</v>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v>Ruta de la imagen</v>
+      </c>
+      <c r="F106" t="str">
+        <v>No nula</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>book_images</v>
+      </c>
+      <c r="B107" t="str">
+        <v>alt_text</v>
+      </c>
+      <c r="C107" t="str">
+        <v>VARCHAR(255)</v>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v>Texto alternativo</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Puede ser nulo</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>book_images</v>
+      </c>
+      <c r="B108" t="str">
+        <v>is_cover</v>
+      </c>
+      <c r="C108" t="str">
+        <v>BOOLEAN</v>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v>Es portada</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Default false</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J108"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1015,11 +4479,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E13"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="48.83203125" customWidth="1"/>
-    <col min="4" max="4" width="58.83203125" customWidth="1"/>
-    <col min="5" max="5" width="34.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1030,13 +4494,13 @@
         <v>Clave primaria</v>
       </c>
       <c r="C1" t="str">
-        <v>Claves foraneas</v>
+        <v>Claves foráneas</v>
       </c>
       <c r="D1" t="str">
         <v>Atributos principales</v>
       </c>
       <c r="E1" t="str">
-        <v>Proposito</v>
+        <v>Propósito</v>
       </c>
     </row>
     <row r="2">
@@ -1053,7 +4517,7 @@
         <v>username, email, password_hash, role</v>
       </c>
       <c r="E2" t="str">
-        <v>Usuarios y administracion</v>
+        <v>Usuarios del sistema</v>
       </c>
     </row>
     <row r="3">
@@ -1070,7 +4534,7 @@
         <v>name, biography, birth_year, country</v>
       </c>
       <c r="E3" t="str">
-        <v>Catalogo de autores</v>
+        <v>Catálogo de autores</v>
       </c>
     </row>
     <row r="4">
@@ -1087,7 +4551,7 @@
         <v>name, description</v>
       </c>
       <c r="E4" t="str">
-        <v>Catalogo de generos</v>
+        <v>Catálogo de géneros</v>
       </c>
     </row>
     <row r="5">
@@ -1104,7 +4568,7 @@
         <v>name, description</v>
       </c>
       <c r="E5" t="str">
-        <v>Catalogo de formatos</v>
+        <v>Catálogo de formatos</v>
       </c>
     </row>
     <row r="6">
@@ -1132,13 +4596,13 @@
         <v>isbn</v>
       </c>
       <c r="C7" t="str">
-        <v>format_id -&gt; formats</v>
+        <v>format_id -&gt; formats(format_id)</v>
       </c>
       <c r="D7" t="str">
         <v>title, description, price, stock, publisher</v>
       </c>
       <c r="E7" t="str">
-        <v>Entidad principal</v>
+        <v>Libro principal</v>
       </c>
     </row>
     <row r="8">
@@ -1149,13 +4613,13 @@
         <v>(isbn, author_id)</v>
       </c>
       <c r="C8" t="str">
-        <v>isbn -&gt; books; author_id -&gt; authors</v>
+        <v>isbn -&gt; books(isbn); author_id -&gt; authors(author_id)</v>
       </c>
       <c r="D8" t="str">
         <v>solo claves</v>
       </c>
       <c r="E8" t="str">
-        <v>Relacion N:M libro-autor</v>
+        <v>Relación N:M libro-autor</v>
       </c>
     </row>
     <row r="9">
@@ -1166,13 +4630,13 @@
         <v>(isbn, genre_id)</v>
       </c>
       <c r="C9" t="str">
-        <v>isbn -&gt; books; genre_id -&gt; genres</v>
+        <v>isbn -&gt; books(isbn); genre_id -&gt; genres(genre_id)</v>
       </c>
       <c r="D9" t="str">
         <v>solo claves</v>
       </c>
       <c r="E9" t="str">
-        <v>Relacion N:M libro-genero</v>
+        <v>Relación N:M libro-género</v>
       </c>
     </row>
     <row r="10">
@@ -1183,13 +4647,13 @@
         <v>(isbn, concept_id)</v>
       </c>
       <c r="C10" t="str">
-        <v>isbn -&gt; books; concept_id -&gt; concepts</v>
+        <v>isbn -&gt; books(isbn); concept_id -&gt; concepts(concept_id)</v>
       </c>
       <c r="D10" t="str">
-        <v>definition, created_at</v>
+        <v>definition</v>
       </c>
       <c r="E10" t="str">
-        <v>Definicion especifica por libro</v>
+        <v>Definición por libro</v>
       </c>
     </row>
     <row r="11">
@@ -1200,13 +4664,13 @@
         <v>image_id</v>
       </c>
       <c r="C11" t="str">
-        <v>isbn -&gt; books</v>
+        <v>isbn -&gt; books(isbn)</v>
       </c>
       <c r="D11" t="str">
         <v>image_url, alt_text, is_cover</v>
       </c>
       <c r="E11" t="str">
-        <v>Portadas e imagenes</v>
+        <v>Portadas e imágenes</v>
       </c>
     </row>
     <row r="12">
@@ -1217,13 +4681,13 @@
         <v>log_id</v>
       </c>
       <c r="C12" t="str">
-        <v>user_id -&gt; users</v>
+        <v>user_id -&gt; users(user_id)</v>
       </c>
       <c r="D12" t="str">
         <v>operation, old_values, new_values</v>
       </c>
       <c r="E12" t="str">
-        <v>Auditoria</v>
+        <v>Auditoría de cambios</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +4704,7 @@
         <v>sess, expire</v>
       </c>
       <c r="E13" t="str">
-        <v>Persistencia de sesiones</v>
+        <v>Sesiones del sistema</v>
       </c>
     </row>
   </sheetData>
@@ -1254,11 +4718,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E11"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" customWidth="1"/>
-    <col min="5" max="5" width="64.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="38.83203125" customWidth="1"/>
+    <col min="5" max="5" width="54.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1272,10 +4736,10 @@
         <v>Destino</v>
       </c>
       <c r="D1" t="str">
-        <v>Implementacion</v>
+        <v>Implementación</v>
       </c>
       <c r="E1" t="str">
-        <v>Justificacion</v>
+        <v>Justificación</v>
       </c>
     </row>
     <row r="2">
@@ -1289,7 +4753,7 @@
         <v>book_authors</v>
       </c>
       <c r="D2" t="str">
-        <v>book_authors.isbn FK</v>
+        <v>book_authors.isbn -&gt; books.isbn</v>
       </c>
       <c r="E2" t="str">
         <v>Un libro puede tener varios autores</v>
@@ -1306,10 +4770,10 @@
         <v>book_authors</v>
       </c>
       <c r="D3" t="str">
-        <v>book_authors.author_id FK</v>
+        <v>book_authors.author_id -&gt; authors.author_id</v>
       </c>
       <c r="E3" t="str">
-        <v>Un autor puede escribir varios libros</v>
+        <v>Un autor puede publicar varios libros</v>
       </c>
     </row>
     <row r="4">
@@ -1323,10 +4787,10 @@
         <v>book_genres</v>
       </c>
       <c r="D4" t="str">
-        <v>book_genres.isbn FK</v>
+        <v>book_genres.isbn -&gt; books.isbn</v>
       </c>
       <c r="E4" t="str">
-        <v>Un libro puede tener varios generos</v>
+        <v>Un libro puede pertenecer a varios géneros</v>
       </c>
     </row>
     <row r="5">
@@ -1340,10 +4804,10 @@
         <v>book_genres</v>
       </c>
       <c r="D5" t="str">
-        <v>book_genres.genre_id FK</v>
+        <v>book_genres.genre_id -&gt; genres.genre_id</v>
       </c>
       <c r="E5" t="str">
-        <v>Un genero puede clasificar varios libros</v>
+        <v>Un género clasifica múltiples libros</v>
       </c>
     </row>
     <row r="6">
@@ -1354,18 +4818,18 @@
         <v>1:N</v>
       </c>
       <c r="C6" t="str">
-        <v>book_images</v>
+        <v>book_concepts</v>
       </c>
       <c r="D6" t="str">
-        <v>book_images.isbn FK</v>
+        <v>book_concepts.isbn -&gt; books.isbn</v>
       </c>
       <c r="E6" t="str">
-        <v>Las imagenes son independientes de autores y generos</v>
+        <v>Cada libro puede definir varios conceptos</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>books</v>
+        <v>concepts</v>
       </c>
       <c r="B7" t="str">
         <v>1:N</v>
@@ -1374,27 +4838,27 @@
         <v>book_concepts</v>
       </c>
       <c r="D7" t="str">
-        <v>book_concepts.isbn FK</v>
+        <v>book_concepts.concept_id -&gt; concepts.concept_id</v>
       </c>
       <c r="E7" t="str">
-        <v>Cada libro puede contextualizar conceptos</v>
+        <v>Un concepto se reutiliza en distintos libros</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>concepts</v>
+        <v>books</v>
       </c>
       <c r="B8" t="str">
         <v>1:N</v>
       </c>
       <c r="C8" t="str">
-        <v>book_concepts</v>
+        <v>book_images</v>
       </c>
       <c r="D8" t="str">
-        <v>book_concepts.concept_id FK</v>
+        <v>book_images.isbn -&gt; books.isbn</v>
       </c>
       <c r="E8" t="str">
-        <v>Un concepto se reutiliza con definiciones por libro</v>
+        <v>Todo libro puede tener varias imágenes</v>
       </c>
     </row>
     <row r="9">
@@ -1408,10 +4872,10 @@
         <v>books</v>
       </c>
       <c r="D9" t="str">
-        <v>books.format_id FK</v>
+        <v>books.format_id -&gt; formats.format_id</v>
       </c>
       <c r="E9" t="str">
-        <v>Catalogo sin duplicar nombre de formato</v>
+        <v>El catálogo de formatos no se duplica</v>
       </c>
     </row>
     <row r="10">
@@ -1422,13 +4886,13 @@
         <v>1:N</v>
       </c>
       <c r="C10" t="str">
-        <v>session</v>
+        <v>audit_log</v>
       </c>
       <c r="D10" t="str">
-        <v>session.sess JSONB</v>
+        <v>audit_log.user_id -&gt; users.user_id</v>
       </c>
       <c r="E10" t="str">
-        <v>Persistencia server-side de sesiones</v>
+        <v>Se guarda el historial de cambios</v>
       </c>
     </row>
     <row r="11">
@@ -1439,13 +4903,13 @@
         <v>1:N</v>
       </c>
       <c r="C11" t="str">
-        <v>audit_log</v>
+        <v>session</v>
       </c>
       <c r="D11" t="str">
-        <v>audit_log.user_id FK</v>
+        <v>session.user_id no aplica</v>
       </c>
       <c r="E11" t="str">
-        <v>Registro de operaciones</v>
+        <v>Se mantiene la sesión del usuario</v>
       </c>
     </row>
   </sheetData>
@@ -1457,12 +4921,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
-    <col min="4" max="4" width="62.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1470,7 +4934,7 @@
         <v>Objeto</v>
       </c>
       <c r="B1" t="str">
-        <v>Restriccion</v>
+        <v>Restricción</v>
       </c>
       <c r="C1" t="str">
         <v>Valor</v>
@@ -1490,49 +4954,49 @@
         <v>isbn</v>
       </c>
       <c r="D2" t="str">
-        <v>Identificador unico del libro</v>
+        <v>Identificador único del libro</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>users</v>
+        <v>books</v>
       </c>
       <c r="B3" t="str">
-        <v>UNIQUE</v>
+        <v>CHECK</v>
       </c>
       <c r="C3" t="str">
-        <v>username y email</v>
+        <v>price &gt;= 0</v>
       </c>
       <c r="D3" t="str">
-        <v>Evitar cuentas duplicadas</v>
+        <v>Impide precios negativos</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>genres</v>
+        <v>books</v>
       </c>
       <c r="B4" t="str">
-        <v>UNIQUE</v>
+        <v>CHECK</v>
       </c>
       <c r="C4" t="str">
-        <v>name</v>
+        <v>stock &gt;= 0</v>
       </c>
       <c r="D4" t="str">
-        <v>Evitar generos duplicados</v>
+        <v>Impide inventario negativo</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>concepts</v>
+        <v>books</v>
       </c>
       <c r="B5" t="str">
-        <v>UNIQUE</v>
+        <v>CHECK</v>
       </c>
       <c r="C5" t="str">
-        <v>name</v>
+        <v>format_type IN (PHYSICAL, DIGITAL)</v>
       </c>
       <c r="D5" t="str">
-        <v>Evitar conceptos duplicados</v>
+        <v>Restringe tipo de edición</v>
       </c>
     </row>
     <row r="6">
@@ -1543,71 +5007,113 @@
         <v>CHECK</v>
       </c>
       <c r="C6" t="str">
-        <v>price &gt;= 0</v>
+        <v>digital_format IN (PDF, EPUB)</v>
       </c>
       <c r="D6" t="str">
-        <v>Evitar precios negativos</v>
+        <v>Restringe formatos digitales válidos</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>books</v>
+        <v>genre</v>
       </c>
       <c r="B7" t="str">
-        <v>CHECK</v>
+        <v>UNIQUE</v>
       </c>
       <c r="C7" t="str">
-        <v>stock &gt;= 0</v>
+        <v>name</v>
       </c>
       <c r="D7" t="str">
-        <v>Evitar inventario negativo</v>
+        <v>Evita duplicados de géneros</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>users</v>
+        <v>concepts</v>
       </c>
       <c r="B8" t="str">
-        <v>UNIQUE INDEX parcial</v>
+        <v>UNIQUE</v>
       </c>
       <c r="C8" t="str">
-        <v>role = ADMIN</v>
+        <v>name</v>
       </c>
       <c r="D8" t="str">
-        <v>Garantizar un solo administrador</v>
+        <v>Evita conceptos repetidos</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Relaciones</v>
+        <v>users</v>
       </c>
       <c r="B9" t="str">
-        <v>FOREIGN KEY</v>
+        <v>UNIQUE</v>
       </c>
       <c r="C9" t="str">
-        <v>ON DELETE CASCADE</v>
+        <v>email</v>
       </c>
       <c r="D9" t="str">
-        <v>Conservar integridad al eliminar libros</v>
+        <v>Evita duplicación de cuentas</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Rendimiento</v>
+        <v>users</v>
       </c>
       <c r="B10" t="str">
-        <v>INDEX</v>
+        <v>UNIQUE INDEX parcial</v>
       </c>
       <c r="C10" t="str">
-        <v>title, price, author_id, genre_id</v>
+        <v>role = ADMIN</v>
       </c>
       <c r="D10" t="str">
-        <v>Optimizar busquedas y relaciones</v>
+        <v>Garantiza un solo administrador</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>book_authors</v>
+      </c>
+      <c r="B11" t="str">
+        <v>PK compuesta</v>
+      </c>
+      <c r="C11" t="str">
+        <v>(isbn, author_id)</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Elimina redundancia por combinación</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>book_genres</v>
+      </c>
+      <c r="B12" t="str">
+        <v>PK compuesta</v>
+      </c>
+      <c r="C12" t="str">
+        <v>(isbn, genre_id)</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Elimina redundancia por combinación</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>book_concepts</v>
+      </c>
+      <c r="B13" t="str">
+        <v>PK compuesta</v>
+      </c>
+      <c r="C13" t="str">
+        <v>(isbn, concept_id)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Mantiene definición del concepto por libro</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
 </worksheet>
 </file>